--- a/MiniTemplate/Datas/convert.xlsx
+++ b/MiniTemplate/Datas/convert.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28785" windowHeight="12975"/>
+    <workbookView windowWidth="21000" windowHeight="7485"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -86,7 +86,7 @@
     <t>林海银匣</t>
   </si>
   <si>
-    <t>1001,5|1004,5|1007,5|2,1</t>
+    <t>1001,1|1004,1|1007,1</t>
   </si>
   <si>
     <t>10001,1</t>
@@ -95,7 +95,7 @@
     <t>林海金匣</t>
   </si>
   <si>
-    <t>1002,3|1005,3|1008,3|2,2</t>
+    <t>1001,3|1004,3|1007,3</t>
   </si>
   <si>
     <t>10002,1</t>
@@ -104,7 +104,7 @@
     <t>林海宝匣</t>
   </si>
   <si>
-    <t>1002,5|1005,5|1008,5|3,1</t>
+    <t>1002,1|1005,1|1008,1</t>
   </si>
   <si>
     <t>20000,1</t>
@@ -113,7 +113,97 @@
     <t>白狒狒灵环</t>
   </si>
   <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>20001,1</t>
+  </si>
+  <si>
+    <t>古石巨人灵环</t>
+  </si>
+  <si>
     <t>2,5</t>
+  </si>
+  <si>
+    <t>20002,1</t>
+  </si>
+  <si>
+    <t>青石巨人灵环</t>
+  </si>
+  <si>
+    <t>2,10|3,1</t>
+  </si>
+  <si>
+    <t>4001,1</t>
+  </si>
+  <si>
+    <t>灵能铜剑</t>
+  </si>
+  <si>
+    <t>1009,5|2,3</t>
+  </si>
+  <si>
+    <t>5001,1</t>
+  </si>
+  <si>
+    <t>灵能铜盔</t>
+  </si>
+  <si>
+    <t>1009,3|2,2</t>
+  </si>
+  <si>
+    <t>6001,1</t>
+  </si>
+  <si>
+    <t>灵能铜甲</t>
+  </si>
+  <si>
+    <t>8001,1</t>
+  </si>
+  <si>
+    <t>灵能铜护腿</t>
+  </si>
+  <si>
+    <t>9001,1</t>
+  </si>
+  <si>
+    <t>灵能铜靴</t>
+  </si>
+  <si>
+    <t>4002,1</t>
+  </si>
+  <si>
+    <t>白银巨剑</t>
+  </si>
+  <si>
+    <t>1010,5|2,10|3,1</t>
+  </si>
+  <si>
+    <t>5002,1</t>
+  </si>
+  <si>
+    <t>灵能银盔</t>
+  </si>
+  <si>
+    <t>1010,3|2,5|3,1</t>
+  </si>
+  <si>
+    <t>6002,1</t>
+  </si>
+  <si>
+    <t>灵能银甲</t>
+  </si>
+  <si>
+    <t>8002,1</t>
+  </si>
+  <si>
+    <t>灵能银护腿</t>
+  </si>
+  <si>
+    <t>9002,1</t>
+  </si>
+  <si>
+    <t>灵能银靴</t>
   </si>
 </sst>
 </file>
@@ -1235,90 +1325,256 @@
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="E9" s="2"/>
-      <c r="F9"/>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
       <c r="G9"/>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="E10" s="2"/>
-      <c r="F10"/>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
       <c r="G10"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="E11" s="3"/>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="E12" s="3"/>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="E13" s="3"/>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="E14" s="3"/>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="E15" s="3"/>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="E16" s="3"/>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="5:8">
-      <c r="E17" s="3"/>
+    <row r="17" spans="2:8">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17">
+        <v>6</v>
+      </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="5:8">
-      <c r="E18" s="3"/>
+    <row r="18" spans="2:8">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="5:8">
-      <c r="E19" s="3"/>
+    <row r="19" spans="2:8">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="5:8">
-      <c r="E20" s="3"/>
+    <row r="20" spans="2:8">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="5:8">
+    <row r="21" spans="2:8">
       <c r="E21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="5:8">
+    <row r="22" spans="2:8">
       <c r="E22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="5:8">
+    <row r="23" spans="2:8">
       <c r="E23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="5:8">
+    <row r="24" spans="2:8">
       <c r="E24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="5:8">
+    <row r="25" spans="2:8">
       <c r="E25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="5:8">
+    <row r="26" spans="2:8">
       <c r="E26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="5:8">
+    <row r="27" spans="2:8">
       <c r="E27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="5:8">
+    <row r="28" spans="2:8">
       <c r="E28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="5:8">
+    <row r="29" spans="2:8">
       <c r="H29" s="3"/>
     </row>
   </sheetData>
